--- a/src/main/resources/data/neoexchange/emc/emc_values.xlsx
+++ b/src/main/resources/data/neoexchange/emc/emc_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\navid\Desktop\NeoExchange\src\main\resources\data\neoexchange\emc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F89620DB-2958-4141-B66C-8923F710F9D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4642C5F9-04B3-44BA-BD0E-5D3C7450FD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5205" yWindow="990" windowWidth="21600" windowHeight="11835" xr2:uid="{7C03ADFC-85EF-45B3-99F9-F8A5E795C138}"/>
   </bookViews>
@@ -22483,7 +22483,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -25532,7 +25532,8 @@
         <v>488</v>
       </c>
       <c r="B382">
-        <v>32</v>
+        <f>B766</f>
+        <v>768</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -28676,7 +28677,8 @@
         <v>638</v>
       </c>
       <c r="B775">
-        <v>784</v>
+        <f>B766</f>
+        <v>768</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.25">
